--- a/specification.xlsx
+++ b/specification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Расчёт ИП" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Шлейфы" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Кабельный журнал" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт ИП" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шлейфы" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабельный журнал" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,11 +624,11 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1 эт. — 22 шт.; 2 эт. — 23 шт.</t>
+          <t>1 эт. — 24 шт.; 2 эт. — 24 шт.</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>600</v>
+        <v>654</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>360</v>
+        <v>192</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -1307,14 +1307,14 @@
         <v>20</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Логика «И»: 1 в ШС1, 1 в ШС2; ИП с УС-02</t>
+          <t>Логика «И» по СП 484 п. 6.4.4: 2 ИП в ШС1, 1 ИП в ШС2</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1334,14 @@
         <v>20</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Логика «И»: 1 в ШС1, 1 в ШС2; ИП с УС-02</t>
+          <t>Логика «И» по СП 484 п. 6.4.4: 2 ИП в ШС1, 1 ИП в ШС2</t>
         </is>
       </c>
     </row>
@@ -1766,14 +1766,14 @@
         <v>14.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Логика «И»: 1 в ШС7, 1 в ШС8; ИП с УС-02</t>
+          <t>Логика «И» по СП 484 п. 6.4.4: 2 ИП в ШС7, 1 ИП в ШС8</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
         <v>236.9</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>2</v>
@@ -1808,7 +1808,7 @@
         <v>254.2</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>2</v>
@@ -1827,7 +1827,7 @@
         <v>491.1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>4</v>
@@ -1913,14 +1913,14 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Архив 8 (1 ИП-А), Архив 9 (1 ИП-А), Каб.10 (2), Бойлерная (2 ИП 101), Подсобное (2)</t>
+          <t>Архив 8 (2 ИП-А), Архив 9 (2 ИП-А), Каб.10 (2), Бойлерная (2 ИП 101), Подсобное (2)</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1 эт. сев. (дубль для логики «И»)</t>
+          <t>1 эт. сев. (дубль логики «И»)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Архив 8 (1 ИП-Б), Архив 9 (1 ИП-Б)</t>
+          <t>Архив 8 (1 ИП-Б), Архив 9 (1 ИП-Б) — только дубль</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ком.отд (2), Каб.дир (2), Кухня (2 ИП 101), Серверная (1 ИП-А), Коридор (3)</t>
+          <t>Ком.отд (2), Каб.дир (2), Кухня (2 ИП 101), Серверная (2 ИП-А), Коридор (5)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.45</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="12">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2 эт. (дубль для логики «И»)</t>
+          <t>2 эт. (дубль логики «И»)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Серверная (1 ИП-Б) + Коридор доп. (2)</t>
+          <t>Серверная (1 ИП-Б) — только дубль</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>8 устройств</t>
+          <t>10 устройств</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ППКП — ШС 2 (1 эт. сев. дубль)</t>
+          <t>ППКП — ШС 2 (1 эт. сев. дубль логики «И»)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2 устройства, логика «И»</t>
+          <t>2 ИП-Б архивов (только дубль)</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>10 устройств</t>
+          <t>13 устройств</t>
         </is>
       </c>
     </row>
@@ -2485,16 +2485,16 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>В МР-15</t>
+          <t>В МР-15, стояк</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>3 устройства</t>
+          <t>1 устройство (ИП-Б серверной)</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>

--- a/specification.xlsx
+++ b/specification.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Аккумуляторная батарея</t>
+          <t>Аккумуляторная батарея (ЗИП)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Встроена в Гранит-12 (резерв ≥ 24 ч)</t>
+          <t>Запасная для Гранит-12 — плановая замена (через 3–5 лет)</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Аккумуляторная батарея</t>
+          <t>Аккумуляторная батарея (ЗИП)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Для РИП-12 (резерв оповещения ≥ 24 ч)</t>
+          <t>Запасная для РИП-12-3/17М — плановая замена (через 3–5 лет)</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Места соединения шлейфов и ответвлений</t>
+          <t>Установка над дверями в коридорах: 1 эт. — 7 (по числу шлейфов ИП и ИПР), 2 эт. — 5</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Извещатель пожарный — выносной устройство световой сигнализации</t>
+          <t>Выносное устройство световой сигнализации</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1014,11 +1014,71 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Для ИП в архивах и серверной (СП 484 п.6.6.13)</t>
+          <t>Только для ИП серверной за подвесным потолком (СП 484 п. 6.6.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Узел уплотнения межэтажного кабельного прохода EI 60</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ПМБК (или ОГНЕТЕРМ)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Огнестойкость не менее EI 60 (СП 4.13130, СП 484 п. 6.7.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Устройство защиты от импульсных перенапряжений (УЗИП)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>УЗИП класс II, 220 В</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>На вводе 220 В питания ППКП и РИП-12</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1185,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>СП 484 п.6.6.5 — мин. 1 ИП при резервировании смежным шлейфом</t>
+          <t>СП 484 п. 6.6.5 — 1 ИП с резервированием извещателями шоурума №7 (ШС 3)</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1779,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Тепловые ИП 101-1А-А3 (наличие пара)</t>
+          <t>Тепловые ИП 101-1А-А3 (преобладающий фактор — тепло от электроплит, СП 484 разд. 6.2 и прил. М)</t>
         </is>
       </c>
     </row>
